--- a/アーカイブ用/第7回/抵抗理論に基づくTKC業務の当てはめ例.xlsx
+++ b/アーカイブ用/第7回/抵抗理論に基づくTKC業務の当てはめ例.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Matsumoto-kobe05\Dropbox\07.TKC\☆☆研修講師\2025年4月～近未来プロジェクト\神戸中央支部\第7回（最終回）\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B2ADF5E-56DD-479F-AA58-1225AA7F8205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F272D91D-094D-420D-AEB5-73CFE20A7D60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="抵抗診断表" sheetId="1" r:id="rId1"/>
+    <sheet name="まとめ" sheetId="1" r:id="rId1"/>
     <sheet name="所長視点" sheetId="2" r:id="rId2"/>
     <sheet name="職員視点" sheetId="3" r:id="rId3"/>
     <sheet name="関与先視点" sheetId="4" r:id="rId4"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="300">
   <si>
     <t>業務</t>
   </si>
@@ -360,9 +360,6 @@
     <t>「リスクだけ増えて報酬に見合わない」と感じる。</t>
   </si>
   <si>
-    <t>対象先の選定基準、記載例、レビュー体制、追加報酬の考え方を整備する。</t>
-  </si>
-  <si>
     <t>件数目標だけを掲げると形式化する。書面添付は巡回監査の品質とセットで考える。</t>
   </si>
   <si>
@@ -529,12 +526,6 @@
   </si>
   <si>
     <t>「計画を作っても社長は見ない」と先回りして諦める。</t>
-  </si>
-  <si>
-    <t>継続MASを単なる帳表作成ではなく、社長と計画を作り、毎月運用する仕組みとして位置づける。</t>
-  </si>
-  <si>
-    <t>関与先が直接触れるソフトとして説明しない。会計事務所と経営者が計画を作り、対話するプロセスとして伝える。</t>
   </si>
   <si>
     <t>決算後説明・過去実績説明で十分という慣れがある。</t>
@@ -979,34 +970,50 @@
     <phoneticPr fontId="5"/>
   </si>
   <si>
-    <t>抵抗理論に基づくTKC業務の当てはめ（GPT-5.5 Thinkingを用いて整理。ご注意の上ご利用ください。）</t>
-    <rPh sb="36" eb="37">
+    <t>抵抗理論に基づくTKC業務の当てはめ例：職員視点（GPT-5.5 Thinkingを用いて整理。ご注意の上ご利用ください。）</t>
+    <rPh sb="18" eb="19">
+      <t>レイ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>抵抗理論に基づくTKC業務の当てはめ例：所長視点（GPT-5.5 Thinkingを用いて整理。ご注意の上ご利用ください。）</t>
+    <rPh sb="18" eb="19">
+      <t>レイ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>抵抗理論に基づくTKC業務の当てはめ例（GPT-5.5 Thinkingを用いて整理。ご注意の上ご利用ください。）</t>
+    <rPh sb="18" eb="19">
+      <t>レイ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
       <t>モチ</t>
     </rPh>
-    <rPh sb="39" eb="41">
+    <rPh sb="40" eb="42">
       <t>セイリ</t>
     </rPh>
-    <rPh sb="43" eb="45">
+    <rPh sb="44" eb="46">
       <t>チュウイ</t>
     </rPh>
-    <rPh sb="46" eb="47">
+    <rPh sb="47" eb="48">
       <t>ウエ</t>
     </rPh>
-    <rPh sb="48" eb="50">
+    <rPh sb="49" eb="51">
       <t>リヨウ</t>
     </rPh>
     <phoneticPr fontId="5"/>
   </si>
   <si>
-    <t>抵抗理論に基づくTKC業務の当てはめ：所長視点（GPT-5.5 Thinkingを用いて整理。ご注意の上ご利用ください。）</t>
+    <t>抵抗理論に基づくTKC業務の当てはめ例：関与先視点（GPT-5.5 Thinkingを用いて整理。ご注意の上ご利用ください。）</t>
+    <rPh sb="18" eb="19">
+      <t>レイ</t>
+    </rPh>
     <phoneticPr fontId="5"/>
   </si>
   <si>
-    <t>抵抗理論に基づくTKC業務の当てはめ：職員視点（GPT-5.5 Thinkingを用いて整理。ご注意の上ご利用ください。）</t>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>抵抗理論に基づくTKC業務の当てはめ：関与先視点（GPT-5.5 Thinkingを用いて整理。ご注意の上ご利用ください。）</t>
+    <t>対象先の選定基準、記載例、レビュー体制、報酬の考え方を整備する。</t>
     <phoneticPr fontId="5"/>
   </si>
 </sst>
@@ -1520,7 +1527,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1532,7 +1539,7 @@
     </row>
     <row r="2" spans="1:8" ht="15.75" thickBot="1">
       <c r="A2" s="4" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1732,7 +1739,7 @@
         <v>9</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>51</v>
@@ -1804,7 +1811,7 @@
     </row>
     <row r="13" spans="1:8" ht="45" customHeight="1">
       <c r="A13" s="11" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B13" s="11" t="s">
         <v>9</v>
@@ -1949,7 +1956,7 @@
         <v>102</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="G18" s="9" t="s">
         <v>104</v>
@@ -1978,10 +1985,10 @@
         <v>110</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="45" customHeight="1">
@@ -1992,22 +1999,22 @@
         <v>16</v>
       </c>
       <c r="C20" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="D20" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="E20" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="E20" s="11" t="s">
+      <c r="F20" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="F20" s="8" t="s">
+      <c r="G20" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="G20" s="9" t="s">
+      <c r="H20" s="10" t="s">
         <v>117</v>
-      </c>
-      <c r="H20" s="10" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="45" customHeight="1">
@@ -2018,334 +2025,334 @@
         <v>23</v>
       </c>
       <c r="C21" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="D21" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="E21" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="E21" s="11" t="s">
+      <c r="F21" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="F21" s="8" t="s">
+      <c r="G21" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="G21" s="9" t="s">
+      <c r="H21" s="10" t="s">
         <v>123</v>
-      </c>
-      <c r="H21" s="10" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="45" customHeight="1">
       <c r="A22" s="11" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B22" s="11" t="s">
         <v>9</v>
       </c>
       <c r="C22" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="D22" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="E22" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="E22" s="11" t="s">
+      <c r="F22" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="F22" s="8" t="s">
+      <c r="G22" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="G22" s="9" t="s">
+      <c r="H22" s="10" t="s">
         <v>130</v>
-      </c>
-      <c r="H22" s="10" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="45" customHeight="1">
       <c r="A23" s="11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B23" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C23" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="D23" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="D23" s="11" t="s">
+      <c r="E23" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="E23" s="11" t="s">
+      <c r="F23" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="F23" s="8" t="s">
+      <c r="G23" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="G23" s="9" t="s">
+      <c r="H23" s="10" t="s">
         <v>136</v>
-      </c>
-      <c r="H23" s="10" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="45" customHeight="1">
       <c r="A24" s="11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B24" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C24" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="D24" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="E24" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="E24" s="11" t="s">
+      <c r="F24" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="F24" s="8" t="s">
+      <c r="G24" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="G24" s="9" t="s">
+      <c r="H24" s="10" t="s">
         <v>142</v>
-      </c>
-      <c r="H24" s="10" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="45" customHeight="1">
       <c r="A25" s="11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B25" s="11" t="s">
         <v>9</v>
       </c>
       <c r="C25" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="D25" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="D25" s="11" t="s">
+      <c r="E25" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="E25" s="11" t="s">
+      <c r="F25" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="F25" s="8" t="s">
+      <c r="G25" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="G25" s="9" t="s">
+      <c r="H25" s="10" t="s">
         <v>149</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="45" customHeight="1">
       <c r="A26" s="11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B26" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C26" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="D26" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="D26" s="11" t="s">
+      <c r="E26" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="E26" s="11" t="s">
+      <c r="F26" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="F26" s="8" t="s">
+      <c r="G26" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="G26" s="9" t="s">
+      <c r="H26" s="10" t="s">
         <v>155</v>
-      </c>
-      <c r="H26" s="10" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="45" customHeight="1">
       <c r="A27" s="11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B27" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C27" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="D27" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="D27" s="11" t="s">
+      <c r="E27" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="E27" s="11" t="s">
+      <c r="F27" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="F27" s="8" t="s">
+      <c r="G27" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="G27" s="9" t="s">
+      <c r="H27" s="10" t="s">
         <v>161</v>
-      </c>
-      <c r="H27" s="10" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="45" customHeight="1">
       <c r="A28" s="11" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B28" s="11" t="s">
         <v>9</v>
       </c>
       <c r="C28" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="D28" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="D28" s="11" t="s">
+      <c r="E28" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="E28" s="11" t="s">
+      <c r="F28" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="F28" s="8" t="s">
-        <v>167</v>
-      </c>
       <c r="G28" s="9" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="45" customHeight="1">
       <c r="A29" s="11" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B29" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C29" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="F29" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="D29" s="11" t="s">
+      <c r="G29" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="E29" s="11" t="s">
+      <c r="H29" s="10" t="s">
         <v>172</v>
-      </c>
-      <c r="F29" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="G29" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="45" customHeight="1">
       <c r="A30" s="11" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B30" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C30" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="F30" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="D30" s="11" t="s">
+      <c r="G30" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="E30" s="11" t="s">
+      <c r="H30" s="10" t="s">
         <v>178</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="G30" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="H30" s="10" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="45" customHeight="1">
       <c r="A31" s="11" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B31" s="11" t="s">
         <v>9</v>
       </c>
       <c r="C31" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="E31" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="F31" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="D31" s="11" t="s">
+      <c r="G31" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="E31" s="11" t="s">
+      <c r="H31" s="10" t="s">
         <v>185</v>
-      </c>
-      <c r="F31" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="G31" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="45" customHeight="1">
       <c r="A32" s="11" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B32" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C32" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="F32" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="D32" s="11" t="s">
+      <c r="G32" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="E32" s="11" t="s">
+      <c r="H32" s="10" t="s">
         <v>191</v>
-      </c>
-      <c r="F32" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="G32" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="H32" s="10" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="45" customHeight="1" thickBot="1">
       <c r="A33" s="11" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B33" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C33" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="E33" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="F33" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="D33" s="11" t="s">
+      <c r="G33" s="17" t="s">
         <v>196</v>
       </c>
-      <c r="E33" s="11" t="s">
+      <c r="H33" s="10" t="s">
         <v>197</v>
-      </c>
-      <c r="F33" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="G33" s="17" t="s">
-        <v>199</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -2367,7 +2374,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="24" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2378,7 +2385,7 @@
     </row>
     <row r="2" spans="1:7" ht="15.75" thickBot="1">
       <c r="A2" s="4" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2542,102 +2549,102 @@
         <v>110</v>
       </c>
       <c r="F9" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="G9" s="10" t="s">
         <v>111</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="72" customHeight="1">
       <c r="A10" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="B10" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="C10" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="D10" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="E10" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="F10" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="G10" s="10" t="s">
         <v>130</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="72" customHeight="1">
       <c r="A11" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="B11" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="C11" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="D11" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="E11" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="F11" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="G11" s="10" t="s">
         <v>149</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="72" customHeight="1">
       <c r="A12" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="B12" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="C12" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="D12" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="E12" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="E12" s="8" t="s">
-        <v>167</v>
-      </c>
       <c r="F12" s="9" t="s">
-        <v>168</v>
+        <v>289</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>169</v>
+        <v>283</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="72" customHeight="1" thickBot="1">
       <c r="A13" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="D13" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="E13" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="F13" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="G13" s="10" t="s">
         <v>185</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="F13" s="17" t="s">
-        <v>187</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>188</v>
       </c>
     </row>
   </sheetData>
@@ -2662,7 +2669,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="24" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2673,7 +2680,7 @@
     </row>
     <row r="2" spans="1:7" ht="15.75" thickBot="1">
       <c r="A2" s="4" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2825,114 +2832,114 @@
         <v>106</v>
       </c>
       <c r="B9" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="C9" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="D9" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="E9" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="F9" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="G9" s="10" t="s">
         <v>117</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="72" customHeight="1">
       <c r="A10" s="11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B10" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="C10" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="D10" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="E10" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="F10" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="G10" s="10" t="s">
         <v>136</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="72" customHeight="1">
       <c r="A11" s="11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B11" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="C11" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="D11" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="E11" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="F11" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="G11" s="10" t="s">
         <v>155</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="72" customHeight="1">
       <c r="A12" s="11" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B12" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="E12" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="F12" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="G12" s="10" t="s">
         <v>172</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="72" customHeight="1" thickBot="1">
       <c r="A13" s="11" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B13" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="E13" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="F13" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="G13" s="10" t="s">
         <v>191</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="F13" s="17" t="s">
-        <v>193</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -2954,7 +2961,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="24" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2965,7 +2972,7 @@
     </row>
     <row r="2" spans="1:7" ht="15.75" thickBot="1">
       <c r="A2" s="4" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3117,114 +3124,114 @@
         <v>106</v>
       </c>
       <c r="B9" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="C9" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="D9" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="E9" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="F9" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="G9" s="10" t="s">
         <v>123</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="72" customHeight="1">
       <c r="A10" s="11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B10" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="C10" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="D10" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="E10" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="F10" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="G10" s="10" t="s">
         <v>142</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="72" customHeight="1">
       <c r="A11" s="11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B11" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="C11" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="D11" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="E11" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="F11" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="G11" s="10" t="s">
         <v>161</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="72" customHeight="1">
       <c r="A12" s="11" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B12" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="E12" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="F12" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="G12" s="10" t="s">
         <v>178</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="72" customHeight="1" thickBot="1">
       <c r="A13" s="11" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B13" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="E13" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="F13" s="17" t="s">
         <v>196</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="G13" s="10" t="s">
         <v>197</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="F13" s="17" t="s">
-        <v>199</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -3246,7 +3253,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3256,7 +3263,7 @@
     </row>
     <row r="2" spans="1:6" ht="38.1" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3266,19 +3273,19 @@
     </row>
     <row r="3" spans="1:6" ht="27.95" customHeight="1" thickBot="1">
       <c r="A3" s="13" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B3" s="13" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F3" s="13" t="s">
         <v>7</v>
@@ -3292,16 +3299,16 @@
         <v>9</v>
       </c>
       <c r="C4" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="F4" s="12" t="s">
         <v>207</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>209</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="62.1" customHeight="1">
@@ -3312,16 +3319,16 @@
         <v>16</v>
       </c>
       <c r="C5" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="F5" s="11" t="s">
         <v>211</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>212</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>213</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="62.1" customHeight="1">
@@ -3332,16 +3339,16 @@
         <v>23</v>
       </c>
       <c r="C6" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="F6" s="11" t="s">
         <v>215</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>216</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>217</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="62.1" customHeight="1">
@@ -3352,16 +3359,16 @@
         <v>9</v>
       </c>
       <c r="C7" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="F7" s="11" t="s">
         <v>219</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>221</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="62.1" customHeight="1">
@@ -3372,16 +3379,16 @@
         <v>16</v>
       </c>
       <c r="C8" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="F8" s="11" t="s">
         <v>223</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>224</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>225</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="62.1" customHeight="1">
@@ -3392,16 +3399,16 @@
         <v>23</v>
       </c>
       <c r="C9" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="F9" s="11" t="s">
         <v>227</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>228</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="62.1" customHeight="1">
@@ -3412,16 +3419,16 @@
         <v>9</v>
       </c>
       <c r="C10" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="F10" s="11" t="s">
         <v>231</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>232</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>233</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="62.1" customHeight="1">
@@ -3432,16 +3439,16 @@
         <v>16</v>
       </c>
       <c r="C11" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="F11" s="11" t="s">
         <v>235</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>236</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>237</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="62.1" customHeight="1">
@@ -3452,16 +3459,16 @@
         <v>23</v>
       </c>
       <c r="C12" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="F12" s="11" t="s">
         <v>239</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>241</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="62.1" customHeight="1">
@@ -3472,16 +3479,16 @@
         <v>9</v>
       </c>
       <c r="C13" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="F13" s="11" t="s">
         <v>243</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>244</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>245</v>
-      </c>
-      <c r="F13" s="11" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="62.1" customHeight="1">
@@ -3492,16 +3499,16 @@
         <v>16</v>
       </c>
       <c r="C14" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="F14" s="11" t="s">
         <v>247</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>248</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>249</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="62.1" customHeight="1">
@@ -3512,16 +3519,16 @@
         <v>23</v>
       </c>
       <c r="C15" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="F15" s="11" t="s">
         <v>251</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>253</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>254</v>
       </c>
     </row>
   </sheetData>
@@ -3543,16 +3550,16 @@
   <sheetData>
     <row r="1" spans="1:5" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
     </row>
-    <row r="2" spans="1:5" ht="38.1" customHeight="1">
+    <row r="2" spans="1:5" ht="15">
       <c r="A2" s="4" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3561,16 +3568,16 @@
     </row>
     <row r="3" spans="1:5" ht="27.95" customHeight="1" thickBot="1">
       <c r="A3" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="D3" s="13" t="s">
         <v>256</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>257</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>258</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>259</v>
       </c>
       <c r="E3" s="13" t="s">
         <v>7</v>
@@ -3581,16 +3588,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="E4" s="12" t="s">
         <v>260</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>261</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>262</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="72" customHeight="1">
@@ -3598,16 +3605,16 @@
         <v>3</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="72" customHeight="1">
@@ -3615,16 +3622,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="72" customHeight="1">
@@ -3632,33 +3639,33 @@
         <v>5</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="72" customHeight="1">
       <c r="A8" s="11" t="s">
+        <v>270</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="D8" s="11" t="s">
         <v>273</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="E8" s="11" t="s">
         <v>274</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>276</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="72" customHeight="1">
@@ -3666,33 +3673,33 @@
         <v>49</v>
       </c>
       <c r="B9" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="E9" s="11" t="s">
         <v>278</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>279</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>280</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="72" customHeight="1">
       <c r="A10" s="11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B10" s="11" t="s">
+        <v>279</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>280</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="E10" s="11" t="s">
         <v>282</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>283</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>284</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>285</v>
       </c>
     </row>
   </sheetData>

--- a/アーカイブ用/第7回/抵抗理論に基づくTKC業務の当てはめ例.xlsx
+++ b/アーカイブ用/第7回/抵抗理論に基づくTKC業務の当てはめ例.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Matsumoto-kobe05\Dropbox\07.TKC\☆☆研修講師\2025年4月～近未来プロジェクト\神戸中央支部\第7回（最終回）\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F272D91D-094D-420D-AEB5-73CFE20A7D60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47774634-D48A-430D-8D59-C88BFA8265D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="296">
+  <si>
+    <t>ロレン・ノードグレンとデイヴィッド・ションタルの「抵抗理論」に基づき、TKC会員が進めるべき施策について、整理したものです。所在順は、所長 → 職員 → 関与先。抵抗は相手を責めるためではなく、導入設計上の摩擦を見つけるための診断軸です。</t>
+  </si>
   <si>
     <t>業務</t>
   </si>
@@ -336,9 +339,6 @@
     <t>間違いや管理不足を指摘されることへの抵抗感がある。</t>
   </si>
   <si>
-    <t>「監査されている」「細かく口を出される」と感じる。</t>
-  </si>
-  <si>
     <t>巡回監査の目的を、税務調査対策だけでなく早期の問題発見・黒字化支援として説明する。</t>
   </si>
   <si>
@@ -360,6 +360,9 @@
     <t>「リスクだけ増えて報酬に見合わない」と感じる。</t>
   </si>
   <si>
+    <t>対象先の選定基準、記載例、レビュー体制、報酬の考え方を整備する。</t>
+  </si>
+  <si>
     <t>件数目標だけを掲げると形式化する。書面添付は巡回監査の品質とセットで考える。</t>
   </si>
   <si>
@@ -528,6 +531,9 @@
     <t>「計画を作っても社長は見ない」と先回りして諦める。</t>
   </si>
   <si>
+    <t>会計事務所と経営者が対話するプロセスとして伝える。</t>
+  </si>
+  <si>
     <t>決算後説明・過去実績説明で十分という慣れがある。</t>
   </si>
   <si>
@@ -621,6 +627,15 @@
     <t>恐怖訴求だけでは不信感を招く。必要保障額の根拠と現契約との差額を冷静に示す。</t>
   </si>
   <si>
+    <t>ロレン・ノードグレンとデイヴィッド・ションタルの「抵抗理論」に基づき、TKC会員が進めるべき施策について、整理したものです。所長に生じやすい抵抗のみを抽出。業務推進時の説明・教育・面談設計に使用するためのシートです。</t>
+  </si>
+  <si>
+    <t>ロレン・ノードグレンとデイヴィッド・ションタルの「抵抗理論」に基づき、TKC会員が進めるべき施策について、整理したものです。職員に生じやすい抵抗のみを抽出。業務推進時の説明・教育・面談設計に使用するためのシートです。</t>
+  </si>
+  <si>
+    <t>ロレン・ノードグレンとデイヴィッド・ションタルの「抵抗理論」に基づき、TKC会員が進めるべき施策について、整理したものです。関与先に生じやすい抵抗のみを抽出。業務推進時の説明・教育・面談設計に使用するためのシートです。</t>
+  </si>
+  <si>
     <t>抵抗を下げる打ち手テンプレ</t>
   </si>
   <si>
@@ -876,144 +891,32 @@
     <t>金融機関に弱みを見せるという誤解を避け、信用形成の文脈で説明する。</t>
   </si>
   <si>
-    <t>会計事務所と経営者が対話するプロセスとして伝える。</t>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>モニタリング情報サービス</t>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>紙証憑を預かって確認する従来型監査を標準と考えがちである。</t>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>銀行信販データ受信機能</t>
-    <phoneticPr fontId="5"/>
+    <t>抵抗理論に基づくTKC業務の当てはめ例（GPT-5.5 Thinkingを用いて整理。ご注意の上ご利用ください。）</t>
+  </si>
+  <si>
+    <t>「監視されている」「細かく口を出される」と感じる。</t>
+  </si>
+  <si>
+    <t>継続MASを単なる計画書作成ではなく、社長と対話し、予実対比により黒字経営を支援する仕組みとして位置づける。</t>
+  </si>
+  <si>
+    <t>抵抗理論に基づくTKC業務の当てはめ例：所長視点（GPT-5.5 Thinkingを用いて整理。ご注意の上ご利用ください。）</t>
+  </si>
+  <si>
+    <t>抵抗理論に基づくTKC業務の当てはめ例：職員視点（GPT-5.5 Thinkingを用いて整理。ご注意の上ご利用ください。）</t>
+  </si>
+  <si>
+    <t>抵抗理論に基づくTKC業務の当てはめ例：関与先視点（GPT-5.5 Thinkingを用いて整理。ご注意の上ご利用ください。）</t>
+  </si>
+  <si>
+    <t>ロレン・ノードグレンとデイヴィッド・ションタルの「抵抗理論」に基づき、TKC会員が進めるべき施策について、整理したものです。
+4つの抵抗の意味と、TKC業務に読み替える際の注意点を整理しています。参考URLは必要に応じて最新情報を確認してください。</t>
   </si>
   <si>
     <t>「監視されている」「細かく口を出される」と感じる。</t>
     <rPh sb="1" eb="3">
       <t>カンシ</t>
     </rPh>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>対象先の選定基準、記載例、レビュー体制、報酬の考え方を整備する。</t>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>継続MASを単なる計画書作成ではなく、社長と対話し、予実対比により黒字経営を支援する仕組みとして位置づける。</t>
-    <rPh sb="9" eb="12">
-      <t>ケイカクショ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>タイワ</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>ヨジツ</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>タイヒ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>クロジ</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>ケイエイ</t>
-    </rPh>
-    <rPh sb="38" eb="40">
-      <t>シエン</t>
-    </rPh>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>ロレン・ノードグレンとデイヴィッド・ションタルの「抵抗理論」に基づき、TKC会員が進めるべき施策について、整理したものです。
-4つの抵抗の意味と、TKC業務に読み替える際の注意点を整理しています。参考URLは必要に応じて最新情報を確認してください。</t>
-    <rPh sb="25" eb="27">
-      <t>テイコウ</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>リロン</t>
-    </rPh>
-    <rPh sb="31" eb="32">
-      <t>モト</t>
-    </rPh>
-    <rPh sb="38" eb="40">
-      <t>カイイン</t>
-    </rPh>
-    <rPh sb="41" eb="42">
-      <t>スス</t>
-    </rPh>
-    <rPh sb="46" eb="48">
-      <t>セサク</t>
-    </rPh>
-    <rPh sb="53" eb="55">
-      <t>セイリ</t>
-    </rPh>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>ロレン・ノードグレンとデイヴィッド・ションタルの「抵抗理論」に基づき、TKC会員が進めるべき施策について、整理したものです。所在順は、所長 → 職員 → 関与先。抵抗は相手を責めるためではなく、導入設計上の摩擦を見つけるための診断軸です。</t>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>ロレン・ノードグレンとデイヴィッド・ションタルの「抵抗理論」に基づき、TKC会員が進めるべき施策について、整理したものです。所長に生じやすい抵抗のみを抽出。業務推進時の説明・教育・面談設計に使用するためのシートです。</t>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>ロレン・ノードグレンとデイヴィッド・ションタルの「抵抗理論」に基づき、TKC会員が進めるべき施策について、整理したものです。職員に生じやすい抵抗のみを抽出。業務推進時の説明・教育・面談設計に使用するためのシートです。</t>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>ロレン・ノードグレンとデイヴィッド・ションタルの「抵抗理論」に基づき、TKC会員が進めるべき施策について、整理したものです。関与先に生じやすい抵抗のみを抽出。業務推進時の説明・教育・面談設計に使用するためのシートです。</t>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>抵抗理論に基づくTKC業務の当てはめ例：職員視点（GPT-5.5 Thinkingを用いて整理。ご注意の上ご利用ください。）</t>
-    <rPh sb="18" eb="19">
-      <t>レイ</t>
-    </rPh>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>抵抗理論に基づくTKC業務の当てはめ例：所長視点（GPT-5.5 Thinkingを用いて整理。ご注意の上ご利用ください。）</t>
-    <rPh sb="18" eb="19">
-      <t>レイ</t>
-    </rPh>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>抵抗理論に基づくTKC業務の当てはめ例（GPT-5.5 Thinkingを用いて整理。ご注意の上ご利用ください。）</t>
-    <rPh sb="18" eb="19">
-      <t>レイ</t>
-    </rPh>
-    <rPh sb="37" eb="38">
-      <t>モチ</t>
-    </rPh>
-    <rPh sb="40" eb="42">
-      <t>セイリ</t>
-    </rPh>
-    <rPh sb="44" eb="46">
-      <t>チュウイ</t>
-    </rPh>
-    <rPh sb="47" eb="48">
-      <t>ウエ</t>
-    </rPh>
-    <rPh sb="49" eb="51">
-      <t>リヨウ</t>
-    </rPh>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>抵抗理論に基づくTKC業務の当てはめ例：関与先視点（GPT-5.5 Thinkingを用いて整理。ご注意の上ご利用ください。）</t>
-    <rPh sb="18" eb="19">
-      <t>レイ</t>
-    </rPh>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>対象先の選定基準、記載例、レビュー体制、報酬の考え方を整備する。</t>
     <phoneticPr fontId="5"/>
   </si>
 </sst>
@@ -1489,33 +1392,8 @@
 </a:theme>
 </file>
 
-<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
-<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="350" row="2">
-    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </wetp:taskpane>
-</wetp:taskpanes>
-</file>
-
-<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
-<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{A9C06A8B-5F6F-483E-8FA5-F286A2DD7C0B}">
-  <we:reference id="wa200009404" version="1.0.0.8" store="en-US" storeType="OMEX"/>
-  <we:alternateReferences>
-    <we:reference id="WA200009404" version="1.0.0.8" store="" storeType="OMEX"/>
-  </we:alternateReferences>
-  <we:properties>
-    <we:property name="claude.fileId" value="&quot;d4855588-5d76-4fe5-aff4-158317cdc1e4&quot;"/>
-  </we:properties>
-  <we:bindings/>
-  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</we:webextension>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
   <dimension ref="A1:H33"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -1527,7 +1405,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1537,9 +1415,9 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
     </row>
-    <row r="2" spans="1:8" ht="15.75" thickBot="1">
+    <row r="2" spans="1:8" ht="15">
       <c r="A2" s="4" t="s">
-        <v>291</v>
+        <v>0</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1549,414 +1427,414 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
     </row>
-    <row r="3" spans="1:8" ht="27.95" customHeight="1" thickBot="1">
+    <row r="3" spans="1:8" ht="27.95" customHeight="1">
       <c r="A3" s="13" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="45" customHeight="1">
       <c r="A4" s="12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="45" customHeight="1">
       <c r="A5" s="11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="45" customHeight="1">
       <c r="A6" s="11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="45" customHeight="1">
       <c r="A7" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="45" customHeight="1">
       <c r="A8" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="45" customHeight="1">
       <c r="A9" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="45" customHeight="1">
       <c r="A10" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>285</v>
+        <v>51</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="45" customHeight="1">
       <c r="A11" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="45" customHeight="1">
       <c r="A12" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="45" customHeight="1">
       <c r="A13" s="11" t="s">
-        <v>286</v>
+        <v>69</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="45" customHeight="1">
       <c r="A14" s="11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="45" customHeight="1">
       <c r="A15" s="11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="45" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="45" customHeight="1">
       <c r="A17" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="45" customHeight="1">
       <c r="A18" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="G18" s="9" t="s">
         <v>104</v>
@@ -1970,7 +1848,7 @@
         <v>106</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C19" s="11" t="s">
         <v>107</v>
@@ -1985,10 +1863,10 @@
         <v>110</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>288</v>
+        <v>111</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="45" customHeight="1">
@@ -1996,25 +1874,25 @@
         <v>106</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="45" customHeight="1">
@@ -2022,343 +1900,342 @@
         <v>106</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="45" customHeight="1">
       <c r="A22" s="11" t="s">
-        <v>284</v>
+        <v>125</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="45" customHeight="1">
       <c r="A23" s="11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="45" customHeight="1">
       <c r="A24" s="11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="45" customHeight="1">
       <c r="A25" s="11" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="45" customHeight="1">
       <c r="A26" s="11" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="45" customHeight="1">
       <c r="A27" s="11" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="45" customHeight="1">
       <c r="A28" s="11" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>283</v>
+        <v>168</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="45" customHeight="1">
       <c r="A29" s="11" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="45" customHeight="1">
       <c r="A30" s="11" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="45" customHeight="1">
       <c r="A31" s="11" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="45" customHeight="1">
       <c r="A32" s="11" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="45" customHeight="1" thickBot="1">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="45" customHeight="1">
       <c r="A33" s="11" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="G33" s="17" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="5"/>
-  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.35433070866141736" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="8" scale="71" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -2374,7 +2251,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="24" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2383,9 +2260,9 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
     </row>
-    <row r="2" spans="1:7" ht="15.75" thickBot="1">
+    <row r="2" spans="1:7" ht="15">
       <c r="A2" s="4" t="s">
-        <v>292</v>
+        <v>200</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2394,142 +2271,142 @@
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
     </row>
-    <row r="3" spans="1:7" ht="27.95" customHeight="1" thickBot="1">
+    <row r="3" spans="1:7" ht="27.95" customHeight="1">
       <c r="A3" s="13" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="72" customHeight="1">
       <c r="A4" s="12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="72" customHeight="1">
       <c r="A5" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="72" customHeight="1">
       <c r="A6" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="72" customHeight="1">
       <c r="A7" s="11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="72" customHeight="1">
       <c r="A8" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="72" customHeight="1">
@@ -2549,116 +2426,112 @@
         <v>110</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>299</v>
+        <v>111</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="72" customHeight="1">
       <c r="A10" s="11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="72" customHeight="1">
       <c r="A11" s="11" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="72" customHeight="1">
       <c r="A12" s="11" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="72" customHeight="1" thickBot="1">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="72" customHeight="1">
       <c r="A13" s="11" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="5"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
   <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -2669,7 +2542,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="24" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2678,9 +2551,9 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
     </row>
-    <row r="2" spans="1:7" ht="15.75" thickBot="1">
+    <row r="2" spans="1:7" ht="15">
       <c r="A2" s="4" t="s">
-        <v>293</v>
+        <v>201</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2689,142 +2562,142 @@
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
     </row>
-    <row r="3" spans="1:7" ht="27.95" customHeight="1" thickBot="1">
+    <row r="3" spans="1:7" ht="27.95" customHeight="1">
       <c r="A3" s="13" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="72" customHeight="1">
       <c r="A4" s="12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="72" customHeight="1">
       <c r="A5" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="72" customHeight="1">
       <c r="A6" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="72" customHeight="1">
       <c r="A7" s="11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="72" customHeight="1">
       <c r="A8" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="72" customHeight="1">
@@ -2832,120 +2705,119 @@
         <v>106</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="72" customHeight="1">
       <c r="A10" s="11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="72" customHeight="1">
       <c r="A11" s="11" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="72" customHeight="1">
       <c r="A12" s="11" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="72" customHeight="1" thickBot="1">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="72" customHeight="1">
       <c r="A13" s="11" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="5"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="8" scale="70" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2961,7 +2833,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="24" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2970,9 +2842,9 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
     </row>
-    <row r="2" spans="1:7" ht="15.75" thickBot="1">
+    <row r="2" spans="1:7" ht="15">
       <c r="A2" s="4" t="s">
-        <v>294</v>
+        <v>202</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2981,136 +2853,136 @@
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
     </row>
-    <row r="3" spans="1:7" ht="27.95" customHeight="1" thickBot="1">
+    <row r="3" spans="1:7" ht="27.95" customHeight="1">
       <c r="A3" s="13" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="72" customHeight="1">
       <c r="A4" s="12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="72" customHeight="1">
       <c r="A5" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="72" customHeight="1">
       <c r="A6" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="72" customHeight="1">
       <c r="A7" s="11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="72" customHeight="1">
       <c r="A8" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>103</v>
+        <v>295</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>104</v>
@@ -3124,114 +2996,114 @@
         <v>106</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="72" customHeight="1">
       <c r="A10" s="11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="72" customHeight="1">
       <c r="A11" s="11" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="72" customHeight="1">
       <c r="A12" s="11" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="72" customHeight="1" thickBot="1">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="72" customHeight="1">
       <c r="A13" s="11" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>
@@ -3253,7 +3125,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3263,7 +3135,7 @@
     </row>
     <row r="2" spans="1:6" ht="38.1" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3271,264 +3143,264 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
     </row>
-    <row r="3" spans="1:6" ht="27.95" customHeight="1" thickBot="1">
+    <row r="3" spans="1:6" ht="27.95" customHeight="1">
       <c r="A3" s="13" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="62.1" customHeight="1">
       <c r="A4" s="12" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="62.1" customHeight="1">
       <c r="A5" s="11" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="62.1" customHeight="1">
       <c r="A6" s="11" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="62.1" customHeight="1">
       <c r="A7" s="11" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="62.1" customHeight="1">
       <c r="A8" s="11" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="62.1" customHeight="1">
       <c r="A9" s="11" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="62.1" customHeight="1">
       <c r="A10" s="11" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="62.1" customHeight="1">
       <c r="A11" s="11" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="62.1" customHeight="1">
       <c r="A12" s="11" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="62.1" customHeight="1">
       <c r="A13" s="11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="62.1" customHeight="1">
       <c r="A14" s="11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="62.1" customHeight="1">
       <c r="A15" s="11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
     </row>
   </sheetData>
@@ -3550,7 +3422,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3559,152 +3431,151 @@
     </row>
     <row r="2" spans="1:5" ht="15">
       <c r="A2" s="4" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:5" ht="27.95" customHeight="1" thickBot="1">
+    <row r="3" spans="1:5" ht="27.95" customHeight="1">
       <c r="A3" s="13" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="72" customHeight="1">
       <c r="A4" s="12" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="72" customHeight="1">
       <c r="A5" s="11" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="72" customHeight="1">
       <c r="A6" s="11" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>270</v>
+      </c>
+      <c r="D6" s="11" t="s">
         <v>264</v>
       </c>
-      <c r="C6" s="11" t="s">
-        <v>265</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>259</v>
-      </c>
       <c r="E6" s="11" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="72" customHeight="1">
       <c r="A7" s="11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="72" customHeight="1">
       <c r="A8" s="11" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="72" customHeight="1">
       <c r="A9" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="72" customHeight="1">
       <c r="A10" s="11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="5"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>